--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +542,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>976</v>
+        <v>1337</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-380</v>
+        <v>-752</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>976</v>
+        <v>1337</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-376</v>
+        <v>-257</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,7 +608,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>976</v>
+        <v>1337</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-376</v>
+        <v>-257</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>976</v>
+        <v>1337</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-376</v>
+        <v>-785</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>907</v>
+        <v>1337</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-307</v>
+        <v>-257</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,7 +743,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>907</v>
+        <v>1337</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-307</v>
+        <v>-257</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,507 +788,12 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22-MAY-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>907</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-307</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>585</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>664</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-79</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>585</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-752</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>552</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-785</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>577</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-760</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>585</v>
+        <v>689</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1337</v>
+        <v>888</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-752</v>
+        <v>-199</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -565,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -587,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-257</v>
+        <v>-752</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1080</v>
+        <v>740</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-257</v>
+        <v>-597</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>552</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-785</v>
+        <v>-257</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1080</v>
+        <v>552</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-257</v>
+        <v>-785</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -788,12 +797,57 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-257</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1080</v>
+        <v>861</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-257</v>
+        <v>-476</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>689</v>
+        <v>585</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>888</v>
+        <v>1337</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-199</v>
+        <v>-752</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -574,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-752</v>
+        <v>-257</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>740</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-597</v>
+        <v>-257</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1080</v>
+        <v>552</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-257</v>
+        <v>-785</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>552</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-785</v>
+        <v>-257</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,78 +767,33 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>861</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1337</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-476</v>
+        <v>-257</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>585</v>
+        <v>401</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1337</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-752</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -565,235 +556,10 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>552</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-785</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,33 +551,393 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>401</v>
+        <v>319</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>399</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>-80</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-921</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-592</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-592</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-929</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-837</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-837</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-328</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-52</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
